--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J187-NatureCapacite-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J187-NatureCapacite-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20220527120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-27T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>Place</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Salle</t>
   </si>
   <si>
     <t/>
@@ -379,7 +385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -415,15 +421,23 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
